--- a/用卷/xlsx/1960,1961,1962.xlsx
+++ b/用卷/xlsx/1960,1961,1962.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F0C4F9-635D-48CC-B4E9-91E62FF0AEF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CC506B-EC51-47FA-AF67-2EEC03E23F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -254,7 +254,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -327,13 +327,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -358,37 +382,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -411,6 +417,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -693,25 +708,25 @@
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.625" customWidth="1"/>
+    <col min="4" max="4" width="29.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="20"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="14"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="20"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="14"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -723,21 +738,21 @@
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="12" t="s">
         <v>48</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="9"/>
+      <c r="C4" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="21"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -746,10 +761,10 @@
       <c r="B5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="15"/>
+      <c r="C5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="22"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -758,10 +773,10 @@
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="10"/>
+      <c r="C6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="22"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
@@ -770,10 +785,10 @@
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="8"/>
+      <c r="C7" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="22"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -782,22 +797,22 @@
       <c r="B8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="9"/>
+      <c r="C8" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="22"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="9"/>
+      <c r="C9" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="22"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
@@ -806,10 +821,10 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="9"/>
+      <c r="C10" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="22"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
@@ -818,22 +833,22 @@
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="10"/>
+      <c r="C11" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="22"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="18" t="s">
+      <c r="A12" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="18"/>
+      <c r="C12" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="22"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
@@ -842,10 +857,10 @@
       <c r="B13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="17"/>
+      <c r="C13" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="22"/>
     </row>
     <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -854,10 +869,10 @@
       <c r="B14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="17"/>
+      <c r="C14" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="22"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
@@ -866,10 +881,10 @@
       <c r="B15" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="12"/>
+      <c r="C15" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="22"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -878,10 +893,10 @@
       <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="9"/>
+      <c r="C16" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="23"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
@@ -890,24 +905,24 @@
       <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="18" t="s">
+      <c r="C17" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="11" t="s">
+      <c r="A18" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="11"/>
+      <c r="D18" s="21"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
@@ -916,10 +931,10 @@
       <c r="B19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="9"/>
+      <c r="C19" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="22"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -928,34 +943,34 @@
       <c r="B20" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="10"/>
+      <c r="C20" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="22"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="17"/>
+      <c r="C21" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="22"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="10"/>
+      <c r="C22" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="22"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
@@ -964,10 +979,10 @@
       <c r="B23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="9"/>
+      <c r="C23" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="22"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -976,10 +991,10 @@
       <c r="B24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="13"/>
+      <c r="C24" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="22"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
@@ -988,10 +1003,10 @@
       <c r="B25" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="9"/>
+      <c r="C25" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="22"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
@@ -1000,10 +1015,10 @@
       <c r="B26" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" s="11"/>
+      <c r="C26" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="22"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
@@ -1012,10 +1027,10 @@
       <c r="B27" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="9"/>
+      <c r="C27" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="22"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
@@ -1024,10 +1039,10 @@
       <c r="B28" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="8"/>
+      <c r="C28" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="22"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -1036,35 +1051,35 @@
       <c r="B29" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" s="11"/>
+      <c r="C29" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="22"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="9" t="s">
+      <c r="A30" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" s="9"/>
+      <c r="C30" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="23"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
       <c r="D32" s="7"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -1137,10 +1152,10 @@
       <c r="C38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="19"/>
+      <c r="D38" s="13"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="15" t="s">
         <v>46</v>
       </c>
       <c r="B39" s="4">
@@ -1149,7 +1164,7 @@
       <c r="C39" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D39" s="19"/>
+      <c r="D39" s="13"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
@@ -1176,10 +1191,12 @@
       <c r="D41" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D4:D16"/>
+    <mergeCell ref="D18:D30"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
